--- a/TESTdata2026-08-03.xlsx
+++ b/TESTdata2026-08-03.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Crypto Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Weekly Quadrant" sheetId="2" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -133,6 +134,3406 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:t>Weekly RSI vs StochRSI - bottom-left = buy candidates</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Weekly</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="1F3864"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Weekly Quadrant'!$B$2:$B$356</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="355"/>
+                <c:pt idx="0">
+                  <c:v>39.3054</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.7393</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.851</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>34.3259</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>31.8332</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34.3261</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30.678</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>42.1583</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.6124</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>38.7457</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>38.8537</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>38.8249</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>34.5467</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>32.7336</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28.1482</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>34.3164</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>56.8459</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>41.9565</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>41.9585</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>27.8116</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>28.2723</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.9219</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>47.4727</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>41.3773</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>42.7278</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>42.498</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36.8806</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>48.6872</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>48.069</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26.5199</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>40.4972</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>40.5757</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>31.5089</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>36.4428</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>40.0375</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>54.0756</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>30.1614</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>41.9824</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38.5687</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>38.4265</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>36.1957</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>30.6488</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>51.85</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>41.8787</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>30.3128</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>32.4194</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>60.3653</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>41.3598</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>29.4908</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46.2054</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>33.8724</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>39.8301</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>39.3054</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>45.7393</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>30.851</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>34.3259</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>31.8332</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>34.3261</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>30.678</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>42.1583</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>31.6124</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>38.7457</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>38.8537</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>38.8249</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>34.5467</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>32.7336</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>28.1482</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>34.3164</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>56.8459</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>41.9565</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>41.9585</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>27.8116</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>28.2723</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>25.9219</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>47.4727</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>41.3773</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>42.7278</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>42.498</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>36.8806</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>48.6872</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>39.3054</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>45.7393</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>30.851</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>34.3259</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>31.8332</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>34.3261</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>30.678</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>42.1583</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>31.6124</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>38.7457</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>38.8537</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>38.8249</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>34.5467</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>32.7336</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>28.1482</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>39.3054</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45.7393</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>30.851</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>34.3259</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>31.8332</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>34.3261</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>30.678</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>42.1583</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>31.6124</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>38.7457</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>38.8537</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>38.8249</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>34.5467</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>32.7336</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>28.1482</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>34.3164</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>56.8459</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>41.9565</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>41.9585</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>27.8116</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>28.2723</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>25.9219</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>47.4727</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>41.3773</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>42.7278</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>42.498</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>36.8806</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>48.6872</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>48.069</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>26.5199</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>40.4972</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>40.5757</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>31.5089</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>36.4428</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>40.0375</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>54.0756</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>30.1614</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>41.9824</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>38.5687</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>38.4265</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>36.1957</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>30.6488</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>51.85</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>41.8787</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>30.3128</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>32.4194</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>60.3653</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>41.3598</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>29.4908</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>46.2054</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>33.8724</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>39.8301</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>39.3054</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>45.7393</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>30.851</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>34.3259</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>31.8332</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>34.3261</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>30.678</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>42.1583</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>31.6124</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>38.7457</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>38.8537</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>38.8249</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>34.5467</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>32.7336</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>28.1482</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>34.3164</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>56.8459</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>41.9565</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>41.9585</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>27.8116</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>28.2723</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>25.9219</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>47.4727</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>41.3773</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>42.7278</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>42.498</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>36.8806</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>48.6872</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>48.069</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>26.5199</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>40.4972</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>40.5757</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>31.5089</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>36.4428</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>40.0375</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>54.0756</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>30.1614</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>41.9824</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>38.5687</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>38.4265</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>36.1957</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>30.6488</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>51.85</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>41.8787</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>30.3128</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>32.4194</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>60.3653</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>41.3598</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>29.4908</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>46.2054</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>33.8724</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>39.8301</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>39.3054</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>45.7393</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>30.851</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>34.3259</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>31.8332</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>34.3261</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>30.678</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>42.1583</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>31.6124</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>38.7457</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>38.8537</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>38.8249</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>34.5467</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>32.7336</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>28.1482</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>34.3164</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>56.8459</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>41.9565</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>41.9585</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>27.8116</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>28.2723</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>25.9219</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>47.4727</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>41.3773</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>42.7278</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>42.498</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>36.8806</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>48.6872</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>48.069</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>26.5199</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>40.4972</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>40.5757</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>31.5089</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>36.4428</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>40.0375</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>54.0756</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>30.1614</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>41.9824</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>38.5687</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>38.4265</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>36.1957</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>30.6488</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>51.85</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>41.8787</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>30.3128</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>32.4194</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>60.3653</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>41.3598</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>29.4908</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>46.2054</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>33.8724</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>39.8301</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>39.3054</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>45.7393</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>30.851</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>34.3259</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>31.8332</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>34.3261</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>30.678</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>42.1583</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>31.6124</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>38.7457</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>38.8537</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>38.8249</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>34.5467</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>32.7336</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>28.1482</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>34.3164</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>56.8459</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>41.9565</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>41.9585</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>27.8116</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>28.2723</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>25.9219</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>47.4727</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>41.3773</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>42.7278</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>42.498</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>36.8806</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>48.6872</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>48.069</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>26.5199</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>40.4972</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>40.5757</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>31.5089</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>36.4428</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>40.0375</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>54.0756</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>30.1614</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>41.9824</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>38.5687</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>38.4265</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>36.1957</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>30.6488</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>51.85</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>41.8787</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>30.3128</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>32.4194</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>60.3653</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>41.3598</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>29.4908</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46.2054</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>33.8724</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>39.8301</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>39.3054</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>45.7393</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>30.851</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>34.3259</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>31.8332</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>34.3261</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>30.678</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>42.1583</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>31.6124</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>38.7457</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>38.8537</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>38.8249</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>34.5467</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>32.7336</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>28.1482</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>34.3164</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>56.8459</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>41.9565</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>41.9585</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>27.8116</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>28.2723</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>25.9219</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>47.4727</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>41.3773</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>42.7278</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>42.498</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>36.8806</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>48.6872</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>48.069</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>26.5199</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>40.4972</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>40.5757</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>31.5089</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>36.4428</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>40.0375</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>54.0756</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>30.1614</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>41.9824</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>38.5687</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>38.4265</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>36.1957</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>30.6488</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>51.85</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>41.8787</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>30.3128</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>32.4194</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>60.3653</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>41.3598</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>29.4908</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>46.2054</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>33.8724</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>39.8301</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Weekly Quadrant'!$C$2:$C$356</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="355"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9108</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2119</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.7487</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.4169</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.313</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.3676</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.1311</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3216</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3252</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.5829</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.0373</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1572</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.0588</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.7219</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.8141</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.7816</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.2295</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.7086</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.013</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.2189</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.6521</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.5925</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.0091</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.2674</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.5293</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.5168</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.1934</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.2707</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.7552</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.621</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.6074</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.1174</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.449</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.031</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.0215</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.2571</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.2639</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.3969</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.6878</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.3821</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.4295</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.3521</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.9108</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.2119</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.7487</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.4169</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.313</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.3676</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.1311</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.3216</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.3252</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.5829</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.0373</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.1572</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.0588</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.7219</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.8141</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.7816</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.2295</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.7086</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.013</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.2189</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.6521</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.5925</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.0091</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.9108</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.2119</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.7487</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.4169</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.313</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.3676</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.1311</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.3216</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.3252</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.5829</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.0373</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.1572</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.9108</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.2119</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.7487</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.4169</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.313</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.3676</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.1311</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.3216</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.3252</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.5829</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.0373</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.1572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.0588</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.7219</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.8141</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.7816</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.2295</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.7086</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.013</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.2189</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.6521</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.5925</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.0091</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.2674</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.5293</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.5168</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.1934</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.2707</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.7552</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.621</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.6074</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.1174</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.449</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.031</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.0215</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.2571</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.2639</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.3969</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.6878</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.3821</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.4295</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.3521</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.9108</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.2119</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.7487</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.4169</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.313</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.3676</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.1311</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.3216</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.3252</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.5829</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.0373</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.1572</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.0588</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.7219</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.8141</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.7816</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.2295</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.7086</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.013</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.2189</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.6521</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.5925</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.0091</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.2674</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.5293</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.5168</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.1934</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.2707</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.7552</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.621</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.6074</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.1174</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.449</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.031</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.0215</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.2571</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.2639</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.3969</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.6878</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.3821</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.4295</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.3521</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.9108</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.2119</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.7487</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.4169</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.313</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.3676</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.1311</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.3216</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.3252</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.5829</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.0373</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.1572</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.0588</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.7219</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.8141</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.7816</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.2295</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.7086</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.013</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.2189</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.6521</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.5925</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.0091</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.2674</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.5293</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.5168</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.1934</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.2707</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.7552</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.621</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.6074</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.1174</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.449</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.031</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.0215</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.2571</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.2639</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.3969</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.6878</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.3821</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.4295</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.3521</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.9108</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.2119</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.7487</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.4169</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.313</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.3676</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.1311</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.3216</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.3252</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.5829</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.0373</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.1572</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.0588</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.7219</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.8141</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.7816</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.2295</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.7086</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.013</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.2189</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.6521</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.5925</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.0091</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.2674</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.5293</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.5168</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.1934</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.2707</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.7552</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.621</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.6074</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.1174</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.449</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.031</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.0215</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.2571</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.2639</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.3969</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.6878</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.3821</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.4295</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.3521</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.9108</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.2119</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.7487</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.4169</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.313</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.3676</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.1311</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.3216</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.3252</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.5829</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.0373</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.1572</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.0588</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.7219</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.8141</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.7816</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.2295</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.7086</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.013</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.2189</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.6521</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.5925</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.0091</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.2674</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.5293</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.5168</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.1934</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.2707</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.7552</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.621</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.6074</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.1174</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.449</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.031</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.0215</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.2571</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.2639</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.3969</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.6878</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.3821</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.4295</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.3521</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'Weekly Quadrant'!$A$2:$A$356</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="355"/>
+                  <c:pt idx="0">
+                    <c:v>ADAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>APEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>APTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>ARBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>ATOMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>AVAXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>BCHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>BNBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>BOMEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>BTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>BTCUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>BTTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>CHZEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>DOGEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>DOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>ENJEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>ETCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>ETHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>ETHUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>GALAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>GMTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>GRTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>HOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>ICPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>JASMYEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>LINKEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>LTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>LUNAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>NEAREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>OPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>PEPEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>PEPEUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>PNUTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>POLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>RENDEREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>RUNEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>SEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="37">
+                    <c:v>SHIBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="38">
+                    <c:v>SOLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="39">
+                    <c:v>SOLUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="40">
+                    <c:v>SUIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="41">
+                    <c:v>TRUMPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="42">
+                    <c:v>TRXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="43">
+                    <c:v>UNIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="44">
+                    <c:v>VETEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="45">
+                    <c:v>WIFEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="46">
+                    <c:v>WINEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="47">
+                    <c:v>WLDEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="48">
+                    <c:v>WLFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="49">
+                    <c:v>XLMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="50">
+                    <c:v>XRPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="51">
+                    <c:v>YFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="52">
+                    <c:v>ADAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="53">
+                    <c:v>APEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="54">
+                    <c:v>APTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="55">
+                    <c:v>ARBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="56">
+                    <c:v>ATOMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="57">
+                    <c:v>AVAXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="58">
+                    <c:v>BCHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="59">
+                    <c:v>BNBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="60">
+                    <c:v>BOMEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="61">
+                    <c:v>BTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="62">
+                    <c:v>BTCUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="63">
+                    <c:v>BTTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="64">
+                    <c:v>CHZEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="65">
+                    <c:v>DOGEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="66">
+                    <c:v>DOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="67">
+                    <c:v>ENJEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="68">
+                    <c:v>ETCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="69">
+                    <c:v>ETHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="70">
+                    <c:v>ETHUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="71">
+                    <c:v>GALAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="72">
+                    <c:v>GMTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="73">
+                    <c:v>GRTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="74">
+                    <c:v>HOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="75">
+                    <c:v>ICPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="76">
+                    <c:v>JASMYEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="77">
+                    <c:v>LINKEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="78">
+                    <c:v>LTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="79">
+                    <c:v>LUNAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="80">
+                    <c:v>ADAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="81">
+                    <c:v>APEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="82">
+                    <c:v>APTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="83">
+                    <c:v>ARBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="84">
+                    <c:v>ATOMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="85">
+                    <c:v>AVAXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="86">
+                    <c:v>BCHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="87">
+                    <c:v>BNBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="88">
+                    <c:v>BOMEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="89">
+                    <c:v>BTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="90">
+                    <c:v>BTCUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="91">
+                    <c:v>BTTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="92">
+                    <c:v>CHZEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="93">
+                    <c:v>DOGEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="94">
+                    <c:v>DOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="95">
+                    <c:v>ADAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="96">
+                    <c:v>APEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="97">
+                    <c:v>APTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="98">
+                    <c:v>ARBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="99">
+                    <c:v>ATOMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="100">
+                    <c:v>AVAXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="101">
+                    <c:v>BCHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="102">
+                    <c:v>BNBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="103">
+                    <c:v>BOMEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="104">
+                    <c:v>BTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="105">
+                    <c:v>BTCUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="106">
+                    <c:v>BTTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="107">
+                    <c:v>CHZEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>DOGEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="109">
+                    <c:v>DOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="110">
+                    <c:v>ENJEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="111">
+                    <c:v>ETCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="112">
+                    <c:v>ETHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="113">
+                    <c:v>ETHUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="114">
+                    <c:v>GALAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="115">
+                    <c:v>GMTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="116">
+                    <c:v>GRTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="117">
+                    <c:v>HOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="118">
+                    <c:v>ICPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="119">
+                    <c:v>JASMYEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="120">
+                    <c:v>LINKEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="121">
+                    <c:v>LTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="122">
+                    <c:v>LUNAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="123">
+                    <c:v>NEAREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="124">
+                    <c:v>OPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="125">
+                    <c:v>PEPEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="126">
+                    <c:v>PEPEUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="127">
+                    <c:v>PNUTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="128">
+                    <c:v>POLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="129">
+                    <c:v>RENDEREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="130">
+                    <c:v>RUNEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="131">
+                    <c:v>SEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="132">
+                    <c:v>SHIBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="133">
+                    <c:v>SOLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="134">
+                    <c:v>SOLUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="135">
+                    <c:v>SUIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="136">
+                    <c:v>TRUMPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="137">
+                    <c:v>TRXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="138">
+                    <c:v>UNIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="139">
+                    <c:v>VETEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="140">
+                    <c:v>WIFEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="141">
+                    <c:v>WINEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="142">
+                    <c:v>WLDEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="143">
+                    <c:v>WLFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="144">
+                    <c:v>XLMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="145">
+                    <c:v>XRPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="146">
+                    <c:v>YFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="147">
+                    <c:v>ADAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="148">
+                    <c:v>APEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="149">
+                    <c:v>APTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="150">
+                    <c:v>ARBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="151">
+                    <c:v>ATOMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="152">
+                    <c:v>AVAXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="153">
+                    <c:v>BCHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="154">
+                    <c:v>BNBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="155">
+                    <c:v>BOMEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="156">
+                    <c:v>BTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="157">
+                    <c:v>BTCUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="158">
+                    <c:v>BTTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="159">
+                    <c:v>CHZEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="160">
+                    <c:v>DOGEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="161">
+                    <c:v>DOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="162">
+                    <c:v>ENJEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="163">
+                    <c:v>ETCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="164">
+                    <c:v>ETHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="165">
+                    <c:v>ETHUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="166">
+                    <c:v>GALAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="167">
+                    <c:v>GMTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="168">
+                    <c:v>GRTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="169">
+                    <c:v>HOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="170">
+                    <c:v>ICPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="171">
+                    <c:v>JASMYEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="172">
+                    <c:v>LINKEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="173">
+                    <c:v>LTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="174">
+                    <c:v>LUNAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="175">
+                    <c:v>NEAREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="176">
+                    <c:v>OPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="177">
+                    <c:v>PEPEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="178">
+                    <c:v>PEPEUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="179">
+                    <c:v>PNUTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="180">
+                    <c:v>POLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="181">
+                    <c:v>RENDEREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="182">
+                    <c:v>RUNEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="183">
+                    <c:v>SEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="184">
+                    <c:v>SHIBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="185">
+                    <c:v>SOLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="186">
+                    <c:v>SOLUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="187">
+                    <c:v>SUIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="188">
+                    <c:v>TRUMPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="189">
+                    <c:v>TRXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="190">
+                    <c:v>UNIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="191">
+                    <c:v>VETEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="192">
+                    <c:v>WIFEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="193">
+                    <c:v>WINEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="194">
+                    <c:v>WLDEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="195">
+                    <c:v>WLFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="196">
+                    <c:v>XLMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="197">
+                    <c:v>XRPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="198">
+                    <c:v>YFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="199">
+                    <c:v>ADAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="200">
+                    <c:v>APEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="201">
+                    <c:v>APTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="202">
+                    <c:v>ARBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="203">
+                    <c:v>ATOMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="204">
+                    <c:v>AVAXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="205">
+                    <c:v>BCHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="206">
+                    <c:v>BNBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="207">
+                    <c:v>BOMEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="208">
+                    <c:v>BTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="209">
+                    <c:v>BTCUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="210">
+                    <c:v>BTTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="211">
+                    <c:v>CHZEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="212">
+                    <c:v>DOGEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="213">
+                    <c:v>DOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="214">
+                    <c:v>ENJEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="215">
+                    <c:v>ETCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="216">
+                    <c:v>ETHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="217">
+                    <c:v>ETHUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="218">
+                    <c:v>GALAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="219">
+                    <c:v>GMTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="220">
+                    <c:v>GRTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="221">
+                    <c:v>HOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="222">
+                    <c:v>ICPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="223">
+                    <c:v>JASMYEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="224">
+                    <c:v>LINKEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="225">
+                    <c:v>LTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="226">
+                    <c:v>LUNAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="227">
+                    <c:v>NEAREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="228">
+                    <c:v>OPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="229">
+                    <c:v>PEPEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="230">
+                    <c:v>PEPEUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="231">
+                    <c:v>PNUTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="232">
+                    <c:v>POLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="233">
+                    <c:v>RENDEREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="234">
+                    <c:v>RUNEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="235">
+                    <c:v>SEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="236">
+                    <c:v>SHIBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="237">
+                    <c:v>SOLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="238">
+                    <c:v>SOLUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="239">
+                    <c:v>SUIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="240">
+                    <c:v>TRUMPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="241">
+                    <c:v>TRXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="242">
+                    <c:v>UNIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="243">
+                    <c:v>VETEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="244">
+                    <c:v>WIFEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="245">
+                    <c:v>WINEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="246">
+                    <c:v>WLDEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="247">
+                    <c:v>WLFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="248">
+                    <c:v>XLMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="249">
+                    <c:v>XRPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="250">
+                    <c:v>YFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="251">
+                    <c:v>ADAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="252">
+                    <c:v>APEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="253">
+                    <c:v>APTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="254">
+                    <c:v>ARBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="255">
+                    <c:v>ATOMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="256">
+                    <c:v>AVAXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="257">
+                    <c:v>BCHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="258">
+                    <c:v>BNBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="259">
+                    <c:v>BOMEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="260">
+                    <c:v>BTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="261">
+                    <c:v>BTCUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="262">
+                    <c:v>BTTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="263">
+                    <c:v>CHZEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="264">
+                    <c:v>DOGEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="265">
+                    <c:v>DOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="266">
+                    <c:v>ENJEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="267">
+                    <c:v>ETCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="268">
+                    <c:v>ETHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="269">
+                    <c:v>ETHUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="270">
+                    <c:v>GALAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="271">
+                    <c:v>GMTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="272">
+                    <c:v>GRTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="273">
+                    <c:v>HOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="274">
+                    <c:v>ICPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="275">
+                    <c:v>JASMYEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="276">
+                    <c:v>LINKEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="277">
+                    <c:v>LTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="278">
+                    <c:v>LUNAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="279">
+                    <c:v>NEAREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="280">
+                    <c:v>OPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="281">
+                    <c:v>PEPEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="282">
+                    <c:v>PEPEUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="283">
+                    <c:v>PNUTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="284">
+                    <c:v>POLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="285">
+                    <c:v>RENDEREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="286">
+                    <c:v>RUNEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="287">
+                    <c:v>SEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="288">
+                    <c:v>SHIBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="289">
+                    <c:v>SOLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="290">
+                    <c:v>SOLUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="291">
+                    <c:v>SUIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="292">
+                    <c:v>TRUMPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="293">
+                    <c:v>TRXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="294">
+                    <c:v>UNIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="295">
+                    <c:v>VETEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="296">
+                    <c:v>WIFEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="297">
+                    <c:v>WINEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="298">
+                    <c:v>WLDEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="299">
+                    <c:v>WLFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="300">
+                    <c:v>XLMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="301">
+                    <c:v>XRPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="302">
+                    <c:v>YFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="303">
+                    <c:v>ADAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="304">
+                    <c:v>APEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="305">
+                    <c:v>APTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="306">
+                    <c:v>ARBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="307">
+                    <c:v>ATOMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="308">
+                    <c:v>AVAXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="309">
+                    <c:v>BCHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="310">
+                    <c:v>BNBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="311">
+                    <c:v>BOMEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="312">
+                    <c:v>BTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="313">
+                    <c:v>BTCUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="314">
+                    <c:v>BTTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="315">
+                    <c:v>CHZEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="316">
+                    <c:v>DOGEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="317">
+                    <c:v>DOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="318">
+                    <c:v>ENJEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="319">
+                    <c:v>ETCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="320">
+                    <c:v>ETHEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="321">
+                    <c:v>ETHUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="322">
+                    <c:v>GALAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="323">
+                    <c:v>GMTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="324">
+                    <c:v>GRTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="325">
+                    <c:v>HOTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="326">
+                    <c:v>ICPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="327">
+                    <c:v>JASMYEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="328">
+                    <c:v>LINKEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="329">
+                    <c:v>LTCEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="330">
+                    <c:v>LUNAEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="331">
+                    <c:v>NEAREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="332">
+                    <c:v>OPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="333">
+                    <c:v>PEPEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="334">
+                    <c:v>PEPEUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="335">
+                    <c:v>PNUTEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="336">
+                    <c:v>POLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="337">
+                    <c:v>RENDEREUR</c:v>
+                  </c:pt>
+                  <c:pt idx="338">
+                    <c:v>RUNEEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="339">
+                    <c:v>SEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="340">
+                    <c:v>SHIBEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="341">
+                    <c:v>SOLEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="342">
+                    <c:v>SOLUSDC</c:v>
+                  </c:pt>
+                  <c:pt idx="343">
+                    <c:v>SUIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="344">
+                    <c:v>TRUMPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="345">
+                    <c:v>TRXEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="346">
+                    <c:v>UNIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="347">
+                    <c:v>VETEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="348">
+                    <c:v>WIFEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="349">
+                    <c:v>WINEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="350">
+                    <c:v>WLDEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="351">
+                    <c:v>WLFIEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="352">
+                    <c:v>XLMEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="353">
+                    <c:v>XRPEUR</c:v>
+                  </c:pt>
+                  <c:pt idx="354">
+                    <c:v>YFIEUR</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:axId val="111111111"/>
+        <c:axId val="222222222"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="111111111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:t>RSI (weekly)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="222222222"/>
+        <c:crossesAt val="50"/>
+        <c:majorUnit val="10"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="222222222"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:t>StochRSI (weekly)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="111111111"/>
+        <c:crossesAt val="0.5"/>
+        <c:majorUnit val="0.1"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Weekly Quadrant Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
@@ -44208,4 +47609,4649 @@
     </cfRule>
   </conditionalFormatting>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StochRSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ADAEUR</t>
+        </is>
+      </c>
+      <c r="B2" s="6">
+        <v>39.3054</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>APEEUR</t>
+        </is>
+      </c>
+      <c r="B3" s="6">
+        <v>45.7393</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.9108</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>APTEUR</t>
+        </is>
+      </c>
+      <c r="B4" s="6">
+        <v>30.851</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.2119</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ARBEUR</t>
+        </is>
+      </c>
+      <c r="B5" s="6">
+        <v>34.3259</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.7487</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ATOMEUR</t>
+        </is>
+      </c>
+      <c r="B6" s="6">
+        <v>31.8332</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AVAXEUR</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <v>34.3261</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BCHEUR</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
+        <v>30.678</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BNBEUR</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <v>42.1583</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BOMEEUR</t>
+        </is>
+      </c>
+      <c r="B10" s="6">
+        <v>31.6124</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.1311</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BTCEUR</t>
+        </is>
+      </c>
+      <c r="B11" s="6">
+        <v>38.7457</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BTCUSDC</t>
+        </is>
+      </c>
+      <c r="B12" s="6">
+        <v>38.8537</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BTTEUR</t>
+        </is>
+      </c>
+      <c r="B13" s="6">
+        <v>38.8249</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.5829</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CHZEUR</t>
+        </is>
+      </c>
+      <c r="B14" s="6">
+        <v>34.5467</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>DOGEEUR</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <v>32.7336</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.0373</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DOTEUR</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
+        <v>28.1482</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.1572</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ENJEUR</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <v>34.3164</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.0588</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ETCEUR</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <v>56.8459</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0.7219</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ETHEUR</t>
+        </is>
+      </c>
+      <c r="B19" s="6">
+        <v>41.9565</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0.8141</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ETHUSDC</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <v>41.9585</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0.7816</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GALAEUR</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <v>27.8116</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GMTEUR</t>
+        </is>
+      </c>
+      <c r="B22" s="6">
+        <v>28.2723</v>
+      </c>
+      <c r="C22" s="8">
+        <v>0.2295</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GRTEUR</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
+        <v>25.9219</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>HOTEUR</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
+        <v>47.4727</v>
+      </c>
+      <c r="C24" s="8">
+        <v>0.7086</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ICPEUR</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <v>41.3773</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>JASMYEUR</t>
+        </is>
+      </c>
+      <c r="B26" s="6">
+        <v>42.7278</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.2189</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LINKEUR</t>
+        </is>
+      </c>
+      <c r="B27" s="6">
+        <v>42.498</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.6521</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LTCEUR</t>
+        </is>
+      </c>
+      <c r="B28" s="6">
+        <v>36.8806</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.5925</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>LUNAEUR</t>
+        </is>
+      </c>
+      <c r="B29" s="6">
+        <v>48.6872</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.0091</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>NEAREUR</t>
+        </is>
+      </c>
+      <c r="B30" s="6">
+        <v>48.069</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0.2674</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>OPEUR</t>
+        </is>
+      </c>
+      <c r="B31" s="6">
+        <v>26.5199</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>PEPEEUR</t>
+        </is>
+      </c>
+      <c r="B32" s="6">
+        <v>40.4972</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0.5293</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>PEPEUSDC</t>
+        </is>
+      </c>
+      <c r="B33" s="6">
+        <v>40.5757</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.5168</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>PNUTEUR</t>
+        </is>
+      </c>
+      <c r="B34" s="6">
+        <v>31.5089</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0.1934</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>POLEUR</t>
+        </is>
+      </c>
+      <c r="B35" s="6">
+        <v>36.4428</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.2707</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RENDEREUR</t>
+        </is>
+      </c>
+      <c r="B36" s="6">
+        <v>40.0375</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RUNEEUR</t>
+        </is>
+      </c>
+      <c r="B37" s="6">
+        <v>54.0756</v>
+      </c>
+      <c r="C37" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SEUR</t>
+        </is>
+      </c>
+      <c r="B38" s="6">
+        <v>30.1614</v>
+      </c>
+      <c r="C38" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SHIBEUR</t>
+        </is>
+      </c>
+      <c r="B39" s="6">
+        <v>41.9824</v>
+      </c>
+      <c r="C39" s="8">
+        <v>0.7552</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SOLEUR</t>
+        </is>
+      </c>
+      <c r="B40" s="6">
+        <v>38.5687</v>
+      </c>
+      <c r="C40" s="8">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SOLUSDC</t>
+        </is>
+      </c>
+      <c r="B41" s="6">
+        <v>38.4265</v>
+      </c>
+      <c r="C41" s="8">
+        <v>0.6074</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SUIEUR</t>
+        </is>
+      </c>
+      <c r="B42" s="6">
+        <v>36.1957</v>
+      </c>
+      <c r="C42" s="8">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TRUMPEUR</t>
+        </is>
+      </c>
+      <c r="B43" s="6">
+        <v>30.6488</v>
+      </c>
+      <c r="C43" s="8">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TRXEUR</t>
+        </is>
+      </c>
+      <c r="B44" s="6">
+        <v>51.85</v>
+      </c>
+      <c r="C44" s="8">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>UNIEUR</t>
+        </is>
+      </c>
+      <c r="B45" s="6">
+        <v>41.8787</v>
+      </c>
+      <c r="C45" s="8">
+        <v>0.0215</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>VETEUR</t>
+        </is>
+      </c>
+      <c r="B46" s="6">
+        <v>30.3128</v>
+      </c>
+      <c r="C46" s="8">
+        <v>0.2571</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>WIFEUR</t>
+        </is>
+      </c>
+      <c r="B47" s="6">
+        <v>32.4194</v>
+      </c>
+      <c r="C47" s="8">
+        <v>0.2639</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>WINEUR</t>
+        </is>
+      </c>
+      <c r="B48" s="6">
+        <v>60.3653</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>WLDEUR</t>
+        </is>
+      </c>
+      <c r="B49" s="6">
+        <v>41.3598</v>
+      </c>
+      <c r="C49" s="8">
+        <v>0.3969</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>WLFIEUR</t>
+        </is>
+      </c>
+      <c r="B50" s="6">
+        <v>29.4908</v>
+      </c>
+      <c r="C50" s="8">
+        <v>0.6878</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>XLMEUR</t>
+        </is>
+      </c>
+      <c r="B51" s="6">
+        <v>46.2054</v>
+      </c>
+      <c r="C51" s="8">
+        <v>0.3821</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>XRPEUR</t>
+        </is>
+      </c>
+      <c r="B52" s="6">
+        <v>33.8724</v>
+      </c>
+      <c r="C52" s="8">
+        <v>0.4295</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>YFIEUR</t>
+        </is>
+      </c>
+      <c r="B53" s="6">
+        <v>39.8301</v>
+      </c>
+      <c r="C53" s="8">
+        <v>0.3521</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ADAEUR</t>
+        </is>
+      </c>
+      <c r="B54" s="6">
+        <v>39.3054</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>APEEUR</t>
+        </is>
+      </c>
+      <c r="B55" s="6">
+        <v>45.7393</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.9108</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>APTEUR</t>
+        </is>
+      </c>
+      <c r="B56" s="6">
+        <v>30.851</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.2119</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ARBEUR</t>
+        </is>
+      </c>
+      <c r="B57" s="6">
+        <v>34.3259</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.7487</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ATOMEUR</t>
+        </is>
+      </c>
+      <c r="B58" s="6">
+        <v>31.8332</v>
+      </c>
+      <c r="C58" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>AVAXEUR</t>
+        </is>
+      </c>
+      <c r="B59" s="6">
+        <v>34.3261</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>BCHEUR</t>
+        </is>
+      </c>
+      <c r="B60" s="6">
+        <v>30.678</v>
+      </c>
+      <c r="C60" s="8">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>BNBEUR</t>
+        </is>
+      </c>
+      <c r="B61" s="6">
+        <v>42.1583</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>BOMEEUR</t>
+        </is>
+      </c>
+      <c r="B62" s="6">
+        <v>31.6124</v>
+      </c>
+      <c r="C62" s="8">
+        <v>0.1311</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>BTCEUR</t>
+        </is>
+      </c>
+      <c r="B63" s="6">
+        <v>38.7457</v>
+      </c>
+      <c r="C63" s="8">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>BTCUSDC</t>
+        </is>
+      </c>
+      <c r="B64" s="6">
+        <v>38.8537</v>
+      </c>
+      <c r="C64" s="8">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>BTTEUR</t>
+        </is>
+      </c>
+      <c r="B65" s="6">
+        <v>38.8249</v>
+      </c>
+      <c r="C65" s="8">
+        <v>0.5829</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CHZEUR</t>
+        </is>
+      </c>
+      <c r="B66" s="6">
+        <v>34.5467</v>
+      </c>
+      <c r="C66" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>DOGEEUR</t>
+        </is>
+      </c>
+      <c r="B67" s="6">
+        <v>32.7336</v>
+      </c>
+      <c r="C67" s="8">
+        <v>0.0373</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>DOTEUR</t>
+        </is>
+      </c>
+      <c r="B68" s="6">
+        <v>28.1482</v>
+      </c>
+      <c r="C68" s="8">
+        <v>0.1572</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ENJEUR</t>
+        </is>
+      </c>
+      <c r="B69" s="6">
+        <v>34.3164</v>
+      </c>
+      <c r="C69" s="8">
+        <v>0.0588</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ETCEUR</t>
+        </is>
+      </c>
+      <c r="B70" s="6">
+        <v>56.8459</v>
+      </c>
+      <c r="C70" s="8">
+        <v>0.7219</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ETHEUR</t>
+        </is>
+      </c>
+      <c r="B71" s="6">
+        <v>41.9565</v>
+      </c>
+      <c r="C71" s="8">
+        <v>0.8141</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ETHUSDC</t>
+        </is>
+      </c>
+      <c r="B72" s="6">
+        <v>41.9585</v>
+      </c>
+      <c r="C72" s="8">
+        <v>0.7816</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GALAEUR</t>
+        </is>
+      </c>
+      <c r="B73" s="6">
+        <v>27.8116</v>
+      </c>
+      <c r="C73" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GMTEUR</t>
+        </is>
+      </c>
+      <c r="B74" s="6">
+        <v>28.2723</v>
+      </c>
+      <c r="C74" s="8">
+        <v>0.2295</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GRTEUR</t>
+        </is>
+      </c>
+      <c r="B75" s="6">
+        <v>25.9219</v>
+      </c>
+      <c r="C75" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>HOTEUR</t>
+        </is>
+      </c>
+      <c r="B76" s="6">
+        <v>47.4727</v>
+      </c>
+      <c r="C76" s="8">
+        <v>0.7086</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ICPEUR</t>
+        </is>
+      </c>
+      <c r="B77" s="6">
+        <v>41.3773</v>
+      </c>
+      <c r="C77" s="8">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>JASMYEUR</t>
+        </is>
+      </c>
+      <c r="B78" s="6">
+        <v>42.7278</v>
+      </c>
+      <c r="C78" s="8">
+        <v>0.2189</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>LINKEUR</t>
+        </is>
+      </c>
+      <c r="B79" s="6">
+        <v>42.498</v>
+      </c>
+      <c r="C79" s="8">
+        <v>0.6521</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>LTCEUR</t>
+        </is>
+      </c>
+      <c r="B80" s="6">
+        <v>36.8806</v>
+      </c>
+      <c r="C80" s="8">
+        <v>0.5925</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>LUNAEUR</t>
+        </is>
+      </c>
+      <c r="B81" s="6">
+        <v>48.6872</v>
+      </c>
+      <c r="C81" s="8">
+        <v>0.0091</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ADAEUR</t>
+        </is>
+      </c>
+      <c r="B82" s="6">
+        <v>39.3054</v>
+      </c>
+      <c r="C82" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>APEEUR</t>
+        </is>
+      </c>
+      <c r="B83" s="6">
+        <v>45.7393</v>
+      </c>
+      <c r="C83" s="8">
+        <v>0.9108</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>APTEUR</t>
+        </is>
+      </c>
+      <c r="B84" s="6">
+        <v>30.851</v>
+      </c>
+      <c r="C84" s="8">
+        <v>0.2119</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ARBEUR</t>
+        </is>
+      </c>
+      <c r="B85" s="6">
+        <v>34.3259</v>
+      </c>
+      <c r="C85" s="8">
+        <v>0.7487</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ATOMEUR</t>
+        </is>
+      </c>
+      <c r="B86" s="6">
+        <v>31.8332</v>
+      </c>
+      <c r="C86" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>AVAXEUR</t>
+        </is>
+      </c>
+      <c r="B87" s="6">
+        <v>34.3261</v>
+      </c>
+      <c r="C87" s="8">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>BCHEUR</t>
+        </is>
+      </c>
+      <c r="B88" s="6">
+        <v>30.678</v>
+      </c>
+      <c r="C88" s="8">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>BNBEUR</t>
+        </is>
+      </c>
+      <c r="B89" s="6">
+        <v>42.1583</v>
+      </c>
+      <c r="C89" s="8">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>BOMEEUR</t>
+        </is>
+      </c>
+      <c r="B90" s="6">
+        <v>31.6124</v>
+      </c>
+      <c r="C90" s="8">
+        <v>0.1311</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>BTCEUR</t>
+        </is>
+      </c>
+      <c r="B91" s="6">
+        <v>38.7457</v>
+      </c>
+      <c r="C91" s="8">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>BTCUSDC</t>
+        </is>
+      </c>
+      <c r="B92" s="6">
+        <v>38.8537</v>
+      </c>
+      <c r="C92" s="8">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>BTTEUR</t>
+        </is>
+      </c>
+      <c r="B93" s="6">
+        <v>38.8249</v>
+      </c>
+      <c r="C93" s="8">
+        <v>0.5829</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>CHZEUR</t>
+        </is>
+      </c>
+      <c r="B94" s="6">
+        <v>34.5467</v>
+      </c>
+      <c r="C94" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>DOGEEUR</t>
+        </is>
+      </c>
+      <c r="B95" s="6">
+        <v>32.7336</v>
+      </c>
+      <c r="C95" s="8">
+        <v>0.0373</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>DOTEUR</t>
+        </is>
+      </c>
+      <c r="B96" s="6">
+        <v>28.1482</v>
+      </c>
+      <c r="C96" s="8">
+        <v>0.1572</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ADAEUR</t>
+        </is>
+      </c>
+      <c r="B97" s="6">
+        <v>39.3054</v>
+      </c>
+      <c r="C97" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>APEEUR</t>
+        </is>
+      </c>
+      <c r="B98" s="6">
+        <v>45.7393</v>
+      </c>
+      <c r="C98" s="8">
+        <v>0.9108</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>APTEUR</t>
+        </is>
+      </c>
+      <c r="B99" s="6">
+        <v>30.851</v>
+      </c>
+      <c r="C99" s="8">
+        <v>0.2119</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ARBEUR</t>
+        </is>
+      </c>
+      <c r="B100" s="6">
+        <v>34.3259</v>
+      </c>
+      <c r="C100" s="8">
+        <v>0.7487</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>ATOMEUR</t>
+        </is>
+      </c>
+      <c r="B101" s="6">
+        <v>31.8332</v>
+      </c>
+      <c r="C101" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>AVAXEUR</t>
+        </is>
+      </c>
+      <c r="B102" s="6">
+        <v>34.3261</v>
+      </c>
+      <c r="C102" s="8">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>BCHEUR</t>
+        </is>
+      </c>
+      <c r="B103" s="6">
+        <v>30.678</v>
+      </c>
+      <c r="C103" s="8">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>BNBEUR</t>
+        </is>
+      </c>
+      <c r="B104" s="6">
+        <v>42.1583</v>
+      </c>
+      <c r="C104" s="8">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>BOMEEUR</t>
+        </is>
+      </c>
+      <c r="B105" s="6">
+        <v>31.6124</v>
+      </c>
+      <c r="C105" s="8">
+        <v>0.1311</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>BTCEUR</t>
+        </is>
+      </c>
+      <c r="B106" s="6">
+        <v>38.7457</v>
+      </c>
+      <c r="C106" s="8">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>BTCUSDC</t>
+        </is>
+      </c>
+      <c r="B107" s="6">
+        <v>38.8537</v>
+      </c>
+      <c r="C107" s="8">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>BTTEUR</t>
+        </is>
+      </c>
+      <c r="B108" s="6">
+        <v>38.8249</v>
+      </c>
+      <c r="C108" s="8">
+        <v>0.5829</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>CHZEUR</t>
+        </is>
+      </c>
+      <c r="B109" s="6">
+        <v>34.5467</v>
+      </c>
+      <c r="C109" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>DOGEEUR</t>
+        </is>
+      </c>
+      <c r="B110" s="6">
+        <v>32.7336</v>
+      </c>
+      <c r="C110" s="8">
+        <v>0.0373</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>DOTEUR</t>
+        </is>
+      </c>
+      <c r="B111" s="6">
+        <v>28.1482</v>
+      </c>
+      <c r="C111" s="8">
+        <v>0.1572</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ENJEUR</t>
+        </is>
+      </c>
+      <c r="B112" s="6">
+        <v>34.3164</v>
+      </c>
+      <c r="C112" s="8">
+        <v>0.0588</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ETCEUR</t>
+        </is>
+      </c>
+      <c r="B113" s="6">
+        <v>56.8459</v>
+      </c>
+      <c r="C113" s="8">
+        <v>0.7219</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ETHEUR</t>
+        </is>
+      </c>
+      <c r="B114" s="6">
+        <v>41.9565</v>
+      </c>
+      <c r="C114" s="8">
+        <v>0.8141</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ETHUSDC</t>
+        </is>
+      </c>
+      <c r="B115" s="6">
+        <v>41.9585</v>
+      </c>
+      <c r="C115" s="8">
+        <v>0.7816</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GALAEUR</t>
+        </is>
+      </c>
+      <c r="B116" s="6">
+        <v>27.8116</v>
+      </c>
+      <c r="C116" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GMTEUR</t>
+        </is>
+      </c>
+      <c r="B117" s="6">
+        <v>28.2723</v>
+      </c>
+      <c r="C117" s="8">
+        <v>0.2295</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GRTEUR</t>
+        </is>
+      </c>
+      <c r="B118" s="6">
+        <v>25.9219</v>
+      </c>
+      <c r="C118" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>HOTEUR</t>
+        </is>
+      </c>
+      <c r="B119" s="6">
+        <v>47.4727</v>
+      </c>
+      <c r="C119" s="8">
+        <v>0.7086</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ICPEUR</t>
+        </is>
+      </c>
+      <c r="B120" s="6">
+        <v>41.3773</v>
+      </c>
+      <c r="C120" s="8">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>JASMYEUR</t>
+        </is>
+      </c>
+      <c r="B121" s="6">
+        <v>42.7278</v>
+      </c>
+      <c r="C121" s="8">
+        <v>0.2189</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>LINKEUR</t>
+        </is>
+      </c>
+      <c r="B122" s="6">
+        <v>42.498</v>
+      </c>
+      <c r="C122" s="8">
+        <v>0.6521</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>LTCEUR</t>
+        </is>
+      </c>
+      <c r="B123" s="6">
+        <v>36.8806</v>
+      </c>
+      <c r="C123" s="8">
+        <v>0.5925</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>LUNAEUR</t>
+        </is>
+      </c>
+      <c r="B124" s="6">
+        <v>48.6872</v>
+      </c>
+      <c r="C124" s="8">
+        <v>0.0091</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>NEAREUR</t>
+        </is>
+      </c>
+      <c r="B125" s="6">
+        <v>48.069</v>
+      </c>
+      <c r="C125" s="8">
+        <v>0.2674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>OPEUR</t>
+        </is>
+      </c>
+      <c r="B126" s="6">
+        <v>26.5199</v>
+      </c>
+      <c r="C126" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>PEPEEUR</t>
+        </is>
+      </c>
+      <c r="B127" s="6">
+        <v>40.4972</v>
+      </c>
+      <c r="C127" s="8">
+        <v>0.5293</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>PEPEUSDC</t>
+        </is>
+      </c>
+      <c r="B128" s="6">
+        <v>40.5757</v>
+      </c>
+      <c r="C128" s="8">
+        <v>0.5168</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>PNUTEUR</t>
+        </is>
+      </c>
+      <c r="B129" s="6">
+        <v>31.5089</v>
+      </c>
+      <c r="C129" s="8">
+        <v>0.1934</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>POLEUR</t>
+        </is>
+      </c>
+      <c r="B130" s="6">
+        <v>36.4428</v>
+      </c>
+      <c r="C130" s="8">
+        <v>0.2707</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>RENDEREUR</t>
+        </is>
+      </c>
+      <c r="B131" s="6">
+        <v>40.0375</v>
+      </c>
+      <c r="C131" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>RUNEEUR</t>
+        </is>
+      </c>
+      <c r="B132" s="6">
+        <v>54.0756</v>
+      </c>
+      <c r="C132" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>SEUR</t>
+        </is>
+      </c>
+      <c r="B133" s="6">
+        <v>30.1614</v>
+      </c>
+      <c r="C133" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SHIBEUR</t>
+        </is>
+      </c>
+      <c r="B134" s="6">
+        <v>41.9824</v>
+      </c>
+      <c r="C134" s="8">
+        <v>0.7552</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>SOLEUR</t>
+        </is>
+      </c>
+      <c r="B135" s="6">
+        <v>38.5687</v>
+      </c>
+      <c r="C135" s="8">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>SOLUSDC</t>
+        </is>
+      </c>
+      <c r="B136" s="6">
+        <v>38.4265</v>
+      </c>
+      <c r="C136" s="8">
+        <v>0.6074</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>SUIEUR</t>
+        </is>
+      </c>
+      <c r="B137" s="6">
+        <v>36.1957</v>
+      </c>
+      <c r="C137" s="8">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>TRUMPEUR</t>
+        </is>
+      </c>
+      <c r="B138" s="6">
+        <v>30.6488</v>
+      </c>
+      <c r="C138" s="8">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>TRXEUR</t>
+        </is>
+      </c>
+      <c r="B139" s="6">
+        <v>51.85</v>
+      </c>
+      <c r="C139" s="8">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>UNIEUR</t>
+        </is>
+      </c>
+      <c r="B140" s="6">
+        <v>41.8787</v>
+      </c>
+      <c r="C140" s="8">
+        <v>0.0215</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>VETEUR</t>
+        </is>
+      </c>
+      <c r="B141" s="6">
+        <v>30.3128</v>
+      </c>
+      <c r="C141" s="8">
+        <v>0.2571</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>WIFEUR</t>
+        </is>
+      </c>
+      <c r="B142" s="6">
+        <v>32.4194</v>
+      </c>
+      <c r="C142" s="8">
+        <v>0.2639</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>WINEUR</t>
+        </is>
+      </c>
+      <c r="B143" s="6">
+        <v>60.3653</v>
+      </c>
+      <c r="C143" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>WLDEUR</t>
+        </is>
+      </c>
+      <c r="B144" s="6">
+        <v>41.3598</v>
+      </c>
+      <c r="C144" s="8">
+        <v>0.3969</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>WLFIEUR</t>
+        </is>
+      </c>
+      <c r="B145" s="6">
+        <v>29.4908</v>
+      </c>
+      <c r="C145" s="8">
+        <v>0.6878</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>XLMEUR</t>
+        </is>
+      </c>
+      <c r="B146" s="6">
+        <v>46.2054</v>
+      </c>
+      <c r="C146" s="8">
+        <v>0.3821</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>XRPEUR</t>
+        </is>
+      </c>
+      <c r="B147" s="6">
+        <v>33.8724</v>
+      </c>
+      <c r="C147" s="8">
+        <v>0.4295</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>YFIEUR</t>
+        </is>
+      </c>
+      <c r="B148" s="6">
+        <v>39.8301</v>
+      </c>
+      <c r="C148" s="8">
+        <v>0.3521</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>ADAEUR</t>
+        </is>
+      </c>
+      <c r="B149" s="6">
+        <v>39.3054</v>
+      </c>
+      <c r="C149" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>APEEUR</t>
+        </is>
+      </c>
+      <c r="B150" s="6">
+        <v>45.7393</v>
+      </c>
+      <c r="C150" s="8">
+        <v>0.9108</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>APTEUR</t>
+        </is>
+      </c>
+      <c r="B151" s="6">
+        <v>30.851</v>
+      </c>
+      <c r="C151" s="8">
+        <v>0.2119</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>ARBEUR</t>
+        </is>
+      </c>
+      <c r="B152" s="6">
+        <v>34.3259</v>
+      </c>
+      <c r="C152" s="8">
+        <v>0.7487</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>ATOMEUR</t>
+        </is>
+      </c>
+      <c r="B153" s="6">
+        <v>31.8332</v>
+      </c>
+      <c r="C153" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>AVAXEUR</t>
+        </is>
+      </c>
+      <c r="B154" s="6">
+        <v>34.3261</v>
+      </c>
+      <c r="C154" s="8">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>BCHEUR</t>
+        </is>
+      </c>
+      <c r="B155" s="6">
+        <v>30.678</v>
+      </c>
+      <c r="C155" s="8">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>BNBEUR</t>
+        </is>
+      </c>
+      <c r="B156" s="6">
+        <v>42.1583</v>
+      </c>
+      <c r="C156" s="8">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>BOMEEUR</t>
+        </is>
+      </c>
+      <c r="B157" s="6">
+        <v>31.6124</v>
+      </c>
+      <c r="C157" s="8">
+        <v>0.1311</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>BTCEUR</t>
+        </is>
+      </c>
+      <c r="B158" s="6">
+        <v>38.7457</v>
+      </c>
+      <c r="C158" s="8">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>BTCUSDC</t>
+        </is>
+      </c>
+      <c r="B159" s="6">
+        <v>38.8537</v>
+      </c>
+      <c r="C159" s="8">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>BTTEUR</t>
+        </is>
+      </c>
+      <c r="B160" s="6">
+        <v>38.8249</v>
+      </c>
+      <c r="C160" s="8">
+        <v>0.5829</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>CHZEUR</t>
+        </is>
+      </c>
+      <c r="B161" s="6">
+        <v>34.5467</v>
+      </c>
+      <c r="C161" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>DOGEEUR</t>
+        </is>
+      </c>
+      <c r="B162" s="6">
+        <v>32.7336</v>
+      </c>
+      <c r="C162" s="8">
+        <v>0.0373</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>DOTEUR</t>
+        </is>
+      </c>
+      <c r="B163" s="6">
+        <v>28.1482</v>
+      </c>
+      <c r="C163" s="8">
+        <v>0.1572</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ENJEUR</t>
+        </is>
+      </c>
+      <c r="B164" s="6">
+        <v>34.3164</v>
+      </c>
+      <c r="C164" s="8">
+        <v>0.0588</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>ETCEUR</t>
+        </is>
+      </c>
+      <c r="B165" s="6">
+        <v>56.8459</v>
+      </c>
+      <c r="C165" s="8">
+        <v>0.7219</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>ETHEUR</t>
+        </is>
+      </c>
+      <c r="B166" s="6">
+        <v>41.9565</v>
+      </c>
+      <c r="C166" s="8">
+        <v>0.8141</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>ETHUSDC</t>
+        </is>
+      </c>
+      <c r="B167" s="6">
+        <v>41.9585</v>
+      </c>
+      <c r="C167" s="8">
+        <v>0.7816</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GALAEUR</t>
+        </is>
+      </c>
+      <c r="B168" s="6">
+        <v>27.8116</v>
+      </c>
+      <c r="C168" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GMTEUR</t>
+        </is>
+      </c>
+      <c r="B169" s="6">
+        <v>28.2723</v>
+      </c>
+      <c r="C169" s="8">
+        <v>0.2295</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GRTEUR</t>
+        </is>
+      </c>
+      <c r="B170" s="6">
+        <v>25.9219</v>
+      </c>
+      <c r="C170" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>HOTEUR</t>
+        </is>
+      </c>
+      <c r="B171" s="6">
+        <v>47.4727</v>
+      </c>
+      <c r="C171" s="8">
+        <v>0.7086</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>ICPEUR</t>
+        </is>
+      </c>
+      <c r="B172" s="6">
+        <v>41.3773</v>
+      </c>
+      <c r="C172" s="8">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>JASMYEUR</t>
+        </is>
+      </c>
+      <c r="B173" s="6">
+        <v>42.7278</v>
+      </c>
+      <c r="C173" s="8">
+        <v>0.2189</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>LINKEUR</t>
+        </is>
+      </c>
+      <c r="B174" s="6">
+        <v>42.498</v>
+      </c>
+      <c r="C174" s="8">
+        <v>0.6521</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>LTCEUR</t>
+        </is>
+      </c>
+      <c r="B175" s="6">
+        <v>36.8806</v>
+      </c>
+      <c r="C175" s="8">
+        <v>0.5925</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>LUNAEUR</t>
+        </is>
+      </c>
+      <c r="B176" s="6">
+        <v>48.6872</v>
+      </c>
+      <c r="C176" s="8">
+        <v>0.0091</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>NEAREUR</t>
+        </is>
+      </c>
+      <c r="B177" s="6">
+        <v>48.069</v>
+      </c>
+      <c r="C177" s="8">
+        <v>0.2674</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>OPEUR</t>
+        </is>
+      </c>
+      <c r="B178" s="6">
+        <v>26.5199</v>
+      </c>
+      <c r="C178" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>PEPEEUR</t>
+        </is>
+      </c>
+      <c r="B179" s="6">
+        <v>40.4972</v>
+      </c>
+      <c r="C179" s="8">
+        <v>0.5293</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>PEPEUSDC</t>
+        </is>
+      </c>
+      <c r="B180" s="6">
+        <v>40.5757</v>
+      </c>
+      <c r="C180" s="8">
+        <v>0.5168</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>PNUTEUR</t>
+        </is>
+      </c>
+      <c r="B181" s="6">
+        <v>31.5089</v>
+      </c>
+      <c r="C181" s="8">
+        <v>0.1934</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>POLEUR</t>
+        </is>
+      </c>
+      <c r="B182" s="6">
+        <v>36.4428</v>
+      </c>
+      <c r="C182" s="8">
+        <v>0.2707</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>RENDEREUR</t>
+        </is>
+      </c>
+      <c r="B183" s="6">
+        <v>40.0375</v>
+      </c>
+      <c r="C183" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>RUNEEUR</t>
+        </is>
+      </c>
+      <c r="B184" s="6">
+        <v>54.0756</v>
+      </c>
+      <c r="C184" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>SEUR</t>
+        </is>
+      </c>
+      <c r="B185" s="6">
+        <v>30.1614</v>
+      </c>
+      <c r="C185" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>SHIBEUR</t>
+        </is>
+      </c>
+      <c r="B186" s="6">
+        <v>41.9824</v>
+      </c>
+      <c r="C186" s="8">
+        <v>0.7552</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>SOLEUR</t>
+        </is>
+      </c>
+      <c r="B187" s="6">
+        <v>38.5687</v>
+      </c>
+      <c r="C187" s="8">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>SOLUSDC</t>
+        </is>
+      </c>
+      <c r="B188" s="6">
+        <v>38.4265</v>
+      </c>
+      <c r="C188" s="8">
+        <v>0.6074</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>SUIEUR</t>
+        </is>
+      </c>
+      <c r="B189" s="6">
+        <v>36.1957</v>
+      </c>
+      <c r="C189" s="8">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>TRUMPEUR</t>
+        </is>
+      </c>
+      <c r="B190" s="6">
+        <v>30.6488</v>
+      </c>
+      <c r="C190" s="8">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>TRXEUR</t>
+        </is>
+      </c>
+      <c r="B191" s="6">
+        <v>51.85</v>
+      </c>
+      <c r="C191" s="8">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>UNIEUR</t>
+        </is>
+      </c>
+      <c r="B192" s="6">
+        <v>41.8787</v>
+      </c>
+      <c r="C192" s="8">
+        <v>0.0215</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>VETEUR</t>
+        </is>
+      </c>
+      <c r="B193" s="6">
+        <v>30.3128</v>
+      </c>
+      <c r="C193" s="8">
+        <v>0.2571</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>WIFEUR</t>
+        </is>
+      </c>
+      <c r="B194" s="6">
+        <v>32.4194</v>
+      </c>
+      <c r="C194" s="8">
+        <v>0.2639</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>WINEUR</t>
+        </is>
+      </c>
+      <c r="B195" s="6">
+        <v>60.3653</v>
+      </c>
+      <c r="C195" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>WLDEUR</t>
+        </is>
+      </c>
+      <c r="B196" s="6">
+        <v>41.3598</v>
+      </c>
+      <c r="C196" s="8">
+        <v>0.3969</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>WLFIEUR</t>
+        </is>
+      </c>
+      <c r="B197" s="6">
+        <v>29.4908</v>
+      </c>
+      <c r="C197" s="8">
+        <v>0.6878</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>XLMEUR</t>
+        </is>
+      </c>
+      <c r="B198" s="6">
+        <v>46.2054</v>
+      </c>
+      <c r="C198" s="8">
+        <v>0.3821</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>XRPEUR</t>
+        </is>
+      </c>
+      <c r="B199" s="6">
+        <v>33.8724</v>
+      </c>
+      <c r="C199" s="8">
+        <v>0.4295</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>YFIEUR</t>
+        </is>
+      </c>
+      <c r="B200" s="6">
+        <v>39.8301</v>
+      </c>
+      <c r="C200" s="8">
+        <v>0.3521</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>ADAEUR</t>
+        </is>
+      </c>
+      <c r="B201" s="6">
+        <v>39.3054</v>
+      </c>
+      <c r="C201" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>APEEUR</t>
+        </is>
+      </c>
+      <c r="B202" s="6">
+        <v>45.7393</v>
+      </c>
+      <c r="C202" s="8">
+        <v>0.9108</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>APTEUR</t>
+        </is>
+      </c>
+      <c r="B203" s="6">
+        <v>30.851</v>
+      </c>
+      <c r="C203" s="8">
+        <v>0.2119</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>ARBEUR</t>
+        </is>
+      </c>
+      <c r="B204" s="6">
+        <v>34.3259</v>
+      </c>
+      <c r="C204" s="8">
+        <v>0.7487</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>ATOMEUR</t>
+        </is>
+      </c>
+      <c r="B205" s="6">
+        <v>31.8332</v>
+      </c>
+      <c r="C205" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>AVAXEUR</t>
+        </is>
+      </c>
+      <c r="B206" s="6">
+        <v>34.3261</v>
+      </c>
+      <c r="C206" s="8">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>BCHEUR</t>
+        </is>
+      </c>
+      <c r="B207" s="6">
+        <v>30.678</v>
+      </c>
+      <c r="C207" s="8">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>BNBEUR</t>
+        </is>
+      </c>
+      <c r="B208" s="6">
+        <v>42.1583</v>
+      </c>
+      <c r="C208" s="8">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>BOMEEUR</t>
+        </is>
+      </c>
+      <c r="B209" s="6">
+        <v>31.6124</v>
+      </c>
+      <c r="C209" s="8">
+        <v>0.1311</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>BTCEUR</t>
+        </is>
+      </c>
+      <c r="B210" s="6">
+        <v>38.7457</v>
+      </c>
+      <c r="C210" s="8">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>BTCUSDC</t>
+        </is>
+      </c>
+      <c r="B211" s="6">
+        <v>38.8537</v>
+      </c>
+      <c r="C211" s="8">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>BTTEUR</t>
+        </is>
+      </c>
+      <c r="B212" s="6">
+        <v>38.8249</v>
+      </c>
+      <c r="C212" s="8">
+        <v>0.5829</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>CHZEUR</t>
+        </is>
+      </c>
+      <c r="B213" s="6">
+        <v>34.5467</v>
+      </c>
+      <c r="C213" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>DOGEEUR</t>
+        </is>
+      </c>
+      <c r="B214" s="6">
+        <v>32.7336</v>
+      </c>
+      <c r="C214" s="8">
+        <v>0.0373</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>DOTEUR</t>
+        </is>
+      </c>
+      <c r="B215" s="6">
+        <v>28.1482</v>
+      </c>
+      <c r="C215" s="8">
+        <v>0.1572</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>ENJEUR</t>
+        </is>
+      </c>
+      <c r="B216" s="6">
+        <v>34.3164</v>
+      </c>
+      <c r="C216" s="8">
+        <v>0.0588</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>ETCEUR</t>
+        </is>
+      </c>
+      <c r="B217" s="6">
+        <v>56.8459</v>
+      </c>
+      <c r="C217" s="8">
+        <v>0.7219</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>ETHEUR</t>
+        </is>
+      </c>
+      <c r="B218" s="6">
+        <v>41.9565</v>
+      </c>
+      <c r="C218" s="8">
+        <v>0.8141</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>ETHUSDC</t>
+        </is>
+      </c>
+      <c r="B219" s="6">
+        <v>41.9585</v>
+      </c>
+      <c r="C219" s="8">
+        <v>0.7816</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>GALAEUR</t>
+        </is>
+      </c>
+      <c r="B220" s="6">
+        <v>27.8116</v>
+      </c>
+      <c r="C220" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>GMTEUR</t>
+        </is>
+      </c>
+      <c r="B221" s="6">
+        <v>28.2723</v>
+      </c>
+      <c r="C221" s="8">
+        <v>0.2295</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>GRTEUR</t>
+        </is>
+      </c>
+      <c r="B222" s="6">
+        <v>25.9219</v>
+      </c>
+      <c r="C222" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>HOTEUR</t>
+        </is>
+      </c>
+      <c r="B223" s="6">
+        <v>47.4727</v>
+      </c>
+      <c r="C223" s="8">
+        <v>0.7086</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>ICPEUR</t>
+        </is>
+      </c>
+      <c r="B224" s="6">
+        <v>41.3773</v>
+      </c>
+      <c r="C224" s="8">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>JASMYEUR</t>
+        </is>
+      </c>
+      <c r="B225" s="6">
+        <v>42.7278</v>
+      </c>
+      <c r="C225" s="8">
+        <v>0.2189</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>LINKEUR</t>
+        </is>
+      </c>
+      <c r="B226" s="6">
+        <v>42.498</v>
+      </c>
+      <c r="C226" s="8">
+        <v>0.6521</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>LTCEUR</t>
+        </is>
+      </c>
+      <c r="B227" s="6">
+        <v>36.8806</v>
+      </c>
+      <c r="C227" s="8">
+        <v>0.5925</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>LUNAEUR</t>
+        </is>
+      </c>
+      <c r="B228" s="6">
+        <v>48.6872</v>
+      </c>
+      <c r="C228" s="8">
+        <v>0.0091</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>NEAREUR</t>
+        </is>
+      </c>
+      <c r="B229" s="6">
+        <v>48.069</v>
+      </c>
+      <c r="C229" s="8">
+        <v>0.2674</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>OPEUR</t>
+        </is>
+      </c>
+      <c r="B230" s="6">
+        <v>26.5199</v>
+      </c>
+      <c r="C230" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>PEPEEUR</t>
+        </is>
+      </c>
+      <c r="B231" s="6">
+        <v>40.4972</v>
+      </c>
+      <c r="C231" s="8">
+        <v>0.5293</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>PEPEUSDC</t>
+        </is>
+      </c>
+      <c r="B232" s="6">
+        <v>40.5757</v>
+      </c>
+      <c r="C232" s="8">
+        <v>0.5168</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>PNUTEUR</t>
+        </is>
+      </c>
+      <c r="B233" s="6">
+        <v>31.5089</v>
+      </c>
+      <c r="C233" s="8">
+        <v>0.1934</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>POLEUR</t>
+        </is>
+      </c>
+      <c r="B234" s="6">
+        <v>36.4428</v>
+      </c>
+      <c r="C234" s="8">
+        <v>0.2707</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>RENDEREUR</t>
+        </is>
+      </c>
+      <c r="B235" s="6">
+        <v>40.0375</v>
+      </c>
+      <c r="C235" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>RUNEEUR</t>
+        </is>
+      </c>
+      <c r="B236" s="6">
+        <v>54.0756</v>
+      </c>
+      <c r="C236" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>SEUR</t>
+        </is>
+      </c>
+      <c r="B237" s="6">
+        <v>30.1614</v>
+      </c>
+      <c r="C237" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>SHIBEUR</t>
+        </is>
+      </c>
+      <c r="B238" s="6">
+        <v>41.9824</v>
+      </c>
+      <c r="C238" s="8">
+        <v>0.7552</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>SOLEUR</t>
+        </is>
+      </c>
+      <c r="B239" s="6">
+        <v>38.5687</v>
+      </c>
+      <c r="C239" s="8">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>SOLUSDC</t>
+        </is>
+      </c>
+      <c r="B240" s="6">
+        <v>38.4265</v>
+      </c>
+      <c r="C240" s="8">
+        <v>0.6074</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>SUIEUR</t>
+        </is>
+      </c>
+      <c r="B241" s="6">
+        <v>36.1957</v>
+      </c>
+      <c r="C241" s="8">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>TRUMPEUR</t>
+        </is>
+      </c>
+      <c r="B242" s="6">
+        <v>30.6488</v>
+      </c>
+      <c r="C242" s="8">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>TRXEUR</t>
+        </is>
+      </c>
+      <c r="B243" s="6">
+        <v>51.85</v>
+      </c>
+      <c r="C243" s="8">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>UNIEUR</t>
+        </is>
+      </c>
+      <c r="B244" s="6">
+        <v>41.8787</v>
+      </c>
+      <c r="C244" s="8">
+        <v>0.0215</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>VETEUR</t>
+        </is>
+      </c>
+      <c r="B245" s="6">
+        <v>30.3128</v>
+      </c>
+      <c r="C245" s="8">
+        <v>0.2571</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>WIFEUR</t>
+        </is>
+      </c>
+      <c r="B246" s="6">
+        <v>32.4194</v>
+      </c>
+      <c r="C246" s="8">
+        <v>0.2639</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>WINEUR</t>
+        </is>
+      </c>
+      <c r="B247" s="6">
+        <v>60.3653</v>
+      </c>
+      <c r="C247" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>WLDEUR</t>
+        </is>
+      </c>
+      <c r="B248" s="6">
+        <v>41.3598</v>
+      </c>
+      <c r="C248" s="8">
+        <v>0.3969</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>WLFIEUR</t>
+        </is>
+      </c>
+      <c r="B249" s="6">
+        <v>29.4908</v>
+      </c>
+      <c r="C249" s="8">
+        <v>0.6878</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>XLMEUR</t>
+        </is>
+      </c>
+      <c r="B250" s="6">
+        <v>46.2054</v>
+      </c>
+      <c r="C250" s="8">
+        <v>0.3821</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>XRPEUR</t>
+        </is>
+      </c>
+      <c r="B251" s="6">
+        <v>33.8724</v>
+      </c>
+      <c r="C251" s="8">
+        <v>0.4295</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>YFIEUR</t>
+        </is>
+      </c>
+      <c r="B252" s="6">
+        <v>39.8301</v>
+      </c>
+      <c r="C252" s="8">
+        <v>0.3521</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>ADAEUR</t>
+        </is>
+      </c>
+      <c r="B253" s="6">
+        <v>39.3054</v>
+      </c>
+      <c r="C253" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>APEEUR</t>
+        </is>
+      </c>
+      <c r="B254" s="6">
+        <v>45.7393</v>
+      </c>
+      <c r="C254" s="8">
+        <v>0.9108</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>APTEUR</t>
+        </is>
+      </c>
+      <c r="B255" s="6">
+        <v>30.851</v>
+      </c>
+      <c r="C255" s="8">
+        <v>0.2119</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>ARBEUR</t>
+        </is>
+      </c>
+      <c r="B256" s="6">
+        <v>34.3259</v>
+      </c>
+      <c r="C256" s="8">
+        <v>0.7487</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>ATOMEUR</t>
+        </is>
+      </c>
+      <c r="B257" s="6">
+        <v>31.8332</v>
+      </c>
+      <c r="C257" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>AVAXEUR</t>
+        </is>
+      </c>
+      <c r="B258" s="6">
+        <v>34.3261</v>
+      </c>
+      <c r="C258" s="8">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>BCHEUR</t>
+        </is>
+      </c>
+      <c r="B259" s="6">
+        <v>30.678</v>
+      </c>
+      <c r="C259" s="8">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>BNBEUR</t>
+        </is>
+      </c>
+      <c r="B260" s="6">
+        <v>42.1583</v>
+      </c>
+      <c r="C260" s="8">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>BOMEEUR</t>
+        </is>
+      </c>
+      <c r="B261" s="6">
+        <v>31.6124</v>
+      </c>
+      <c r="C261" s="8">
+        <v>0.1311</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>BTCEUR</t>
+        </is>
+      </c>
+      <c r="B262" s="6">
+        <v>38.7457</v>
+      </c>
+      <c r="C262" s="8">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>BTCUSDC</t>
+        </is>
+      </c>
+      <c r="B263" s="6">
+        <v>38.8537</v>
+      </c>
+      <c r="C263" s="8">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>BTTEUR</t>
+        </is>
+      </c>
+      <c r="B264" s="6">
+        <v>38.8249</v>
+      </c>
+      <c r="C264" s="8">
+        <v>0.5829</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>CHZEUR</t>
+        </is>
+      </c>
+      <c r="B265" s="6">
+        <v>34.5467</v>
+      </c>
+      <c r="C265" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>DOGEEUR</t>
+        </is>
+      </c>
+      <c r="B266" s="6">
+        <v>32.7336</v>
+      </c>
+      <c r="C266" s="8">
+        <v>0.0373</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>DOTEUR</t>
+        </is>
+      </c>
+      <c r="B267" s="6">
+        <v>28.1482</v>
+      </c>
+      <c r="C267" s="8">
+        <v>0.1572</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>ENJEUR</t>
+        </is>
+      </c>
+      <c r="B268" s="6">
+        <v>34.3164</v>
+      </c>
+      <c r="C268" s="8">
+        <v>0.0588</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>ETCEUR</t>
+        </is>
+      </c>
+      <c r="B269" s="6">
+        <v>56.8459</v>
+      </c>
+      <c r="C269" s="8">
+        <v>0.7219</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>ETHEUR</t>
+        </is>
+      </c>
+      <c r="B270" s="6">
+        <v>41.9565</v>
+      </c>
+      <c r="C270" s="8">
+        <v>0.8141</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>ETHUSDC</t>
+        </is>
+      </c>
+      <c r="B271" s="6">
+        <v>41.9585</v>
+      </c>
+      <c r="C271" s="8">
+        <v>0.7816</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>GALAEUR</t>
+        </is>
+      </c>
+      <c r="B272" s="6">
+        <v>27.8116</v>
+      </c>
+      <c r="C272" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>GMTEUR</t>
+        </is>
+      </c>
+      <c r="B273" s="6">
+        <v>28.2723</v>
+      </c>
+      <c r="C273" s="8">
+        <v>0.2295</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>GRTEUR</t>
+        </is>
+      </c>
+      <c r="B274" s="6">
+        <v>25.9219</v>
+      </c>
+      <c r="C274" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>HOTEUR</t>
+        </is>
+      </c>
+      <c r="B275" s="6">
+        <v>47.4727</v>
+      </c>
+      <c r="C275" s="8">
+        <v>0.7086</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>ICPEUR</t>
+        </is>
+      </c>
+      <c r="B276" s="6">
+        <v>41.3773</v>
+      </c>
+      <c r="C276" s="8">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>JASMYEUR</t>
+        </is>
+      </c>
+      <c r="B277" s="6">
+        <v>42.7278</v>
+      </c>
+      <c r="C277" s="8">
+        <v>0.2189</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>LINKEUR</t>
+        </is>
+      </c>
+      <c r="B278" s="6">
+        <v>42.498</v>
+      </c>
+      <c r="C278" s="8">
+        <v>0.6521</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>LTCEUR</t>
+        </is>
+      </c>
+      <c r="B279" s="6">
+        <v>36.8806</v>
+      </c>
+      <c r="C279" s="8">
+        <v>0.5925</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>LUNAEUR</t>
+        </is>
+      </c>
+      <c r="B280" s="6">
+        <v>48.6872</v>
+      </c>
+      <c r="C280" s="8">
+        <v>0.0091</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>NEAREUR</t>
+        </is>
+      </c>
+      <c r="B281" s="6">
+        <v>48.069</v>
+      </c>
+      <c r="C281" s="8">
+        <v>0.2674</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>OPEUR</t>
+        </is>
+      </c>
+      <c r="B282" s="6">
+        <v>26.5199</v>
+      </c>
+      <c r="C282" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>PEPEEUR</t>
+        </is>
+      </c>
+      <c r="B283" s="6">
+        <v>40.4972</v>
+      </c>
+      <c r="C283" s="8">
+        <v>0.5293</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>PEPEUSDC</t>
+        </is>
+      </c>
+      <c r="B284" s="6">
+        <v>40.5757</v>
+      </c>
+      <c r="C284" s="8">
+        <v>0.5168</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>PNUTEUR</t>
+        </is>
+      </c>
+      <c r="B285" s="6">
+        <v>31.5089</v>
+      </c>
+      <c r="C285" s="8">
+        <v>0.1934</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>POLEUR</t>
+        </is>
+      </c>
+      <c r="B286" s="6">
+        <v>36.4428</v>
+      </c>
+      <c r="C286" s="8">
+        <v>0.2707</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>RENDEREUR</t>
+        </is>
+      </c>
+      <c r="B287" s="6">
+        <v>40.0375</v>
+      </c>
+      <c r="C287" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>RUNEEUR</t>
+        </is>
+      </c>
+      <c r="B288" s="6">
+        <v>54.0756</v>
+      </c>
+      <c r="C288" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>SEUR</t>
+        </is>
+      </c>
+      <c r="B289" s="6">
+        <v>30.1614</v>
+      </c>
+      <c r="C289" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>SHIBEUR</t>
+        </is>
+      </c>
+      <c r="B290" s="6">
+        <v>41.9824</v>
+      </c>
+      <c r="C290" s="8">
+        <v>0.7552</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>SOLEUR</t>
+        </is>
+      </c>
+      <c r="B291" s="6">
+        <v>38.5687</v>
+      </c>
+      <c r="C291" s="8">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>SOLUSDC</t>
+        </is>
+      </c>
+      <c r="B292" s="6">
+        <v>38.4265</v>
+      </c>
+      <c r="C292" s="8">
+        <v>0.6074</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>SUIEUR</t>
+        </is>
+      </c>
+      <c r="B293" s="6">
+        <v>36.1957</v>
+      </c>
+      <c r="C293" s="8">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>TRUMPEUR</t>
+        </is>
+      </c>
+      <c r="B294" s="6">
+        <v>30.6488</v>
+      </c>
+      <c r="C294" s="8">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>TRXEUR</t>
+        </is>
+      </c>
+      <c r="B295" s="6">
+        <v>51.85</v>
+      </c>
+      <c r="C295" s="8">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>UNIEUR</t>
+        </is>
+      </c>
+      <c r="B296" s="6">
+        <v>41.8787</v>
+      </c>
+      <c r="C296" s="8">
+        <v>0.0215</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>VETEUR</t>
+        </is>
+      </c>
+      <c r="B297" s="6">
+        <v>30.3128</v>
+      </c>
+      <c r="C297" s="8">
+        <v>0.2571</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>WIFEUR</t>
+        </is>
+      </c>
+      <c r="B298" s="6">
+        <v>32.4194</v>
+      </c>
+      <c r="C298" s="8">
+        <v>0.2639</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>WINEUR</t>
+        </is>
+      </c>
+      <c r="B299" s="6">
+        <v>60.3653</v>
+      </c>
+      <c r="C299" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>WLDEUR</t>
+        </is>
+      </c>
+      <c r="B300" s="6">
+        <v>41.3598</v>
+      </c>
+      <c r="C300" s="8">
+        <v>0.3969</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>WLFIEUR</t>
+        </is>
+      </c>
+      <c r="B301" s="6">
+        <v>29.4908</v>
+      </c>
+      <c r="C301" s="8">
+        <v>0.6878</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>XLMEUR</t>
+        </is>
+      </c>
+      <c r="B302" s="6">
+        <v>46.2054</v>
+      </c>
+      <c r="C302" s="8">
+        <v>0.3821</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>XRPEUR</t>
+        </is>
+      </c>
+      <c r="B303" s="6">
+        <v>33.8724</v>
+      </c>
+      <c r="C303" s="8">
+        <v>0.4295</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>YFIEUR</t>
+        </is>
+      </c>
+      <c r="B304" s="6">
+        <v>39.8301</v>
+      </c>
+      <c r="C304" s="8">
+        <v>0.3521</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>ADAEUR</t>
+        </is>
+      </c>
+      <c r="B305" s="6">
+        <v>39.3054</v>
+      </c>
+      <c r="C305" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>APEEUR</t>
+        </is>
+      </c>
+      <c r="B306" s="6">
+        <v>45.7393</v>
+      </c>
+      <c r="C306" s="8">
+        <v>0.9108</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>APTEUR</t>
+        </is>
+      </c>
+      <c r="B307" s="6">
+        <v>30.851</v>
+      </c>
+      <c r="C307" s="8">
+        <v>0.2119</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>ARBEUR</t>
+        </is>
+      </c>
+      <c r="B308" s="6">
+        <v>34.3259</v>
+      </c>
+      <c r="C308" s="8">
+        <v>0.7487</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>ATOMEUR</t>
+        </is>
+      </c>
+      <c r="B309" s="6">
+        <v>31.8332</v>
+      </c>
+      <c r="C309" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>AVAXEUR</t>
+        </is>
+      </c>
+      <c r="B310" s="6">
+        <v>34.3261</v>
+      </c>
+      <c r="C310" s="8">
+        <v>0.4169</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>BCHEUR</t>
+        </is>
+      </c>
+      <c r="B311" s="6">
+        <v>30.678</v>
+      </c>
+      <c r="C311" s="8">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>BNBEUR</t>
+        </is>
+      </c>
+      <c r="B312" s="6">
+        <v>42.1583</v>
+      </c>
+      <c r="C312" s="8">
+        <v>0.3676</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>BOMEEUR</t>
+        </is>
+      </c>
+      <c r="B313" s="6">
+        <v>31.6124</v>
+      </c>
+      <c r="C313" s="8">
+        <v>0.1311</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>BTCEUR</t>
+        </is>
+      </c>
+      <c r="B314" s="6">
+        <v>38.7457</v>
+      </c>
+      <c r="C314" s="8">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>BTCUSDC</t>
+        </is>
+      </c>
+      <c r="B315" s="6">
+        <v>38.8537</v>
+      </c>
+      <c r="C315" s="8">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>BTTEUR</t>
+        </is>
+      </c>
+      <c r="B316" s="6">
+        <v>38.8249</v>
+      </c>
+      <c r="C316" s="8">
+        <v>0.5829</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>CHZEUR</t>
+        </is>
+      </c>
+      <c r="B317" s="6">
+        <v>34.5467</v>
+      </c>
+      <c r="C317" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>DOGEEUR</t>
+        </is>
+      </c>
+      <c r="B318" s="6">
+        <v>32.7336</v>
+      </c>
+      <c r="C318" s="8">
+        <v>0.0373</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>DOTEUR</t>
+        </is>
+      </c>
+      <c r="B319" s="6">
+        <v>28.1482</v>
+      </c>
+      <c r="C319" s="8">
+        <v>0.1572</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>ENJEUR</t>
+        </is>
+      </c>
+      <c r="B320" s="6">
+        <v>34.3164</v>
+      </c>
+      <c r="C320" s="8">
+        <v>0.0588</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>ETCEUR</t>
+        </is>
+      </c>
+      <c r="B321" s="6">
+        <v>56.8459</v>
+      </c>
+      <c r="C321" s="8">
+        <v>0.7219</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>ETHEUR</t>
+        </is>
+      </c>
+      <c r="B322" s="6">
+        <v>41.9565</v>
+      </c>
+      <c r="C322" s="8">
+        <v>0.8141</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>ETHUSDC</t>
+        </is>
+      </c>
+      <c r="B323" s="6">
+        <v>41.9585</v>
+      </c>
+      <c r="C323" s="8">
+        <v>0.7816</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>GALAEUR</t>
+        </is>
+      </c>
+      <c r="B324" s="6">
+        <v>27.8116</v>
+      </c>
+      <c r="C324" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>GMTEUR</t>
+        </is>
+      </c>
+      <c r="B325" s="6">
+        <v>28.2723</v>
+      </c>
+      <c r="C325" s="8">
+        <v>0.2295</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>GRTEUR</t>
+        </is>
+      </c>
+      <c r="B326" s="6">
+        <v>25.9219</v>
+      </c>
+      <c r="C326" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>HOTEUR</t>
+        </is>
+      </c>
+      <c r="B327" s="6">
+        <v>47.4727</v>
+      </c>
+      <c r="C327" s="8">
+        <v>0.7086</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>ICPEUR</t>
+        </is>
+      </c>
+      <c r="B328" s="6">
+        <v>41.3773</v>
+      </c>
+      <c r="C328" s="8">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>JASMYEUR</t>
+        </is>
+      </c>
+      <c r="B329" s="6">
+        <v>42.7278</v>
+      </c>
+      <c r="C329" s="8">
+        <v>0.2189</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>LINKEUR</t>
+        </is>
+      </c>
+      <c r="B330" s="6">
+        <v>42.498</v>
+      </c>
+      <c r="C330" s="8">
+        <v>0.6521</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>LTCEUR</t>
+        </is>
+      </c>
+      <c r="B331" s="6">
+        <v>36.8806</v>
+      </c>
+      <c r="C331" s="8">
+        <v>0.5925</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>LUNAEUR</t>
+        </is>
+      </c>
+      <c r="B332" s="6">
+        <v>48.6872</v>
+      </c>
+      <c r="C332" s="8">
+        <v>0.0091</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>NEAREUR</t>
+        </is>
+      </c>
+      <c r="B333" s="6">
+        <v>48.069</v>
+      </c>
+      <c r="C333" s="8">
+        <v>0.2674</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>OPEUR</t>
+        </is>
+      </c>
+      <c r="B334" s="6">
+        <v>26.5199</v>
+      </c>
+      <c r="C334" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>PEPEEUR</t>
+        </is>
+      </c>
+      <c r="B335" s="6">
+        <v>40.4972</v>
+      </c>
+      <c r="C335" s="8">
+        <v>0.5293</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>PEPEUSDC</t>
+        </is>
+      </c>
+      <c r="B336" s="6">
+        <v>40.5757</v>
+      </c>
+      <c r="C336" s="8">
+        <v>0.5168</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>PNUTEUR</t>
+        </is>
+      </c>
+      <c r="B337" s="6">
+        <v>31.5089</v>
+      </c>
+      <c r="C337" s="8">
+        <v>0.1934</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>POLEUR</t>
+        </is>
+      </c>
+      <c r="B338" s="6">
+        <v>36.4428</v>
+      </c>
+      <c r="C338" s="8">
+        <v>0.2707</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>RENDEREUR</t>
+        </is>
+      </c>
+      <c r="B339" s="6">
+        <v>40.0375</v>
+      </c>
+      <c r="C339" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>RUNEEUR</t>
+        </is>
+      </c>
+      <c r="B340" s="6">
+        <v>54.0756</v>
+      </c>
+      <c r="C340" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>SEUR</t>
+        </is>
+      </c>
+      <c r="B341" s="6">
+        <v>30.1614</v>
+      </c>
+      <c r="C341" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>SHIBEUR</t>
+        </is>
+      </c>
+      <c r="B342" s="6">
+        <v>41.9824</v>
+      </c>
+      <c r="C342" s="8">
+        <v>0.7552</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>SOLEUR</t>
+        </is>
+      </c>
+      <c r="B343" s="6">
+        <v>38.5687</v>
+      </c>
+      <c r="C343" s="8">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>SOLUSDC</t>
+        </is>
+      </c>
+      <c r="B344" s="6">
+        <v>38.4265</v>
+      </c>
+      <c r="C344" s="8">
+        <v>0.6074</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>SUIEUR</t>
+        </is>
+      </c>
+      <c r="B345" s="6">
+        <v>36.1957</v>
+      </c>
+      <c r="C345" s="8">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>TRUMPEUR</t>
+        </is>
+      </c>
+      <c r="B346" s="6">
+        <v>30.6488</v>
+      </c>
+      <c r="C346" s="8">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>TRXEUR</t>
+        </is>
+      </c>
+      <c r="B347" s="6">
+        <v>51.85</v>
+      </c>
+      <c r="C347" s="8">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>UNIEUR</t>
+        </is>
+      </c>
+      <c r="B348" s="6">
+        <v>41.8787</v>
+      </c>
+      <c r="C348" s="8">
+        <v>0.0215</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>VETEUR</t>
+        </is>
+      </c>
+      <c r="B349" s="6">
+        <v>30.3128</v>
+      </c>
+      <c r="C349" s="8">
+        <v>0.2571</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>WIFEUR</t>
+        </is>
+      </c>
+      <c r="B350" s="6">
+        <v>32.4194</v>
+      </c>
+      <c r="C350" s="8">
+        <v>0.2639</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>WINEUR</t>
+        </is>
+      </c>
+      <c r="B351" s="6">
+        <v>60.3653</v>
+      </c>
+      <c r="C351" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>WLDEUR</t>
+        </is>
+      </c>
+      <c r="B352" s="6">
+        <v>41.3598</v>
+      </c>
+      <c r="C352" s="8">
+        <v>0.3969</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>WLFIEUR</t>
+        </is>
+      </c>
+      <c r="B353" s="6">
+        <v>29.4908</v>
+      </c>
+      <c r="C353" s="8">
+        <v>0.6878</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>XLMEUR</t>
+        </is>
+      </c>
+      <c r="B354" s="6">
+        <v>46.2054</v>
+      </c>
+      <c r="C354" s="8">
+        <v>0.3821</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>XRPEUR</t>
+        </is>
+      </c>
+      <c r="B355" s="6">
+        <v>33.8724</v>
+      </c>
+      <c r="C355" s="8">
+        <v>0.4295</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>YFIEUR</t>
+        </is>
+      </c>
+      <c r="B356" s="6">
+        <v>39.8301</v>
+      </c>
+      <c r="C356" s="8">
+        <v>0.3521</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>